--- a/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
+++ b/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard_fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DB9699-F8A0-46A7-ADC8-A654BBA5A2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60FCE06-89A2-4DA0-A106-0C2E0E502021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3945,13 +3945,13 @@
         <v>380</v>
       </c>
       <c r="C3">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3965,13 +3965,13 @@
         <v>381</v>
       </c>
       <c r="C4">
-        <v>200000</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3985,13 +3985,13 @@
         <v>382</v>
       </c>
       <c r="C5">
-        <v>150000</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4061,19 +4061,19 @@
         <v>389</v>
       </c>
       <c r="C3">
-        <v>47304</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>2100</v>
+        <v>10000</v>
       </c>
       <c r="G3">
-        <v>2100</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
+++ b/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard_fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678E980D-974F-455D-8CEE-FCABD6DBA153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4136E517-E5A9-4AF4-BBF2-C5ACC1D926EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="392">
   <si>
     <t>id</t>
   </si>
@@ -1211,6 +1211,9 @@
   </si>
   <si>
     <t>Battery_swap</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -4049,8 +4052,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>24</v>
+      <c r="G3" t="s">
+        <v>391</v>
       </c>
       <c r="H3">
         <v>10000</v>

--- a/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
+++ b/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard_fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD3BF10-776C-4AAA-8907-B59C06A3C8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F77E09A-3E43-49D4-A89D-BA9ECA1068AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
+++ b/data/data_chuqui_3mb_onboard_fixed/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard_fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4136E517-E5A9-4AF4-BBF2-C5ACC1D926EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A809ABEC-7A5B-405F-A70C-4ABB830CC2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="391">
   <si>
     <t>id</t>
   </si>
@@ -1211,9 +1211,6 @@
   </si>
   <si>
     <t>Battery_swap</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
 </sst>
 </file>
@@ -4052,8 +4049,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="s">
-        <v>391</v>
+      <c r="G3">
+        <v>12</v>
       </c>
       <c r="H3">
         <v>10000</v>
